--- a/20251230_youtube_summaries.xlsx
+++ b/20251230_youtube_summaries.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-12-30 09:53</t>
+          <t>2025-12-30 21:17</t>
         </is>
       </c>
     </row>

--- a/20251230_youtube_summaries.xlsx
+++ b/20251230_youtube_summaries.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-12-30 21:17</t>
+          <t>2025-12-30 21:21</t>
         </is>
       </c>
     </row>
